--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_doom_council_info[终焉议会信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_doom_council_info[终焉议会信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25860" windowHeight="8820"/>
   </bookViews>
   <sheets>
     <sheet name="DoomCouncilInfo" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <t>name[language]</t>
   </si>
   <si>
-    <t>details[language]</t>
+    <t>details[language_1]</t>
   </si>
   <si>
     <t>remark</t>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>27</v>
@@ -1296,10 +1296,10 @@
         <v>100200003</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>28</v>
@@ -1328,10 +1328,10 @@
         <v>30</v>
       </c>
       <c r="I6">
-        <v>100001</v>
+        <v>1000000001</v>
       </c>
       <c r="J6">
-        <v>100002</v>
+        <v>1000000001</v>
       </c>
       <c r="K6" t="s">
         <v>31</v>
@@ -1360,10 +1360,10 @@
         <v>30</v>
       </c>
       <c r="I7">
-        <v>100003</v>
+        <v>1000100001</v>
       </c>
       <c r="J7">
-        <v>100004</v>
+        <v>1000100001</v>
       </c>
       <c r="K7" t="s">
         <v>33</v>
@@ -1395,10 +1395,10 @@
         <v>300100201</v>
       </c>
       <c r="I8">
-        <v>200001</v>
+        <v>1000200001</v>
       </c>
       <c r="J8">
-        <v>200002</v>
+        <v>1000200001</v>
       </c>
       <c r="K8" t="s">
         <v>35</v>
@@ -1430,10 +1430,10 @@
         <v>300200201</v>
       </c>
       <c r="I9">
-        <v>200003</v>
+        <v>1000200002</v>
       </c>
       <c r="J9">
-        <v>200004</v>
+        <v>1000200002</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>36</v>
@@ -1465,10 +1465,10 @@
         <v>300300201</v>
       </c>
       <c r="I10">
-        <v>200005</v>
+        <v>1000200003</v>
       </c>
       <c r="J10">
-        <v>200006</v>
+        <v>1000200003</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>37</v>
@@ -1500,10 +1500,10 @@
         <v>300400201</v>
       </c>
       <c r="I11">
-        <v>200007</v>
+        <v>1000200004</v>
       </c>
       <c r="J11">
-        <v>200008</v>
+        <v>1000200004</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>38</v>
@@ -1535,10 +1535,10 @@
         <v>300500201</v>
       </c>
       <c r="I12">
-        <v>200009</v>
+        <v>1000200005</v>
       </c>
       <c r="J12">
-        <v>200010</v>
+        <v>1000200005</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>39</v>
@@ -1570,10 +1570,10 @@
         <v>300600201</v>
       </c>
       <c r="I13">
-        <v>200011</v>
+        <v>1000200006</v>
       </c>
       <c r="J13">
-        <v>200012</v>
+        <v>1000200006</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>40</v>
@@ -1605,10 +1605,10 @@
         <v>300700201</v>
       </c>
       <c r="I14">
-        <v>200013</v>
+        <v>1000200007</v>
       </c>
       <c r="J14">
-        <v>200014</v>
+        <v>1000200007</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>41</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_doom_council_info[终焉议会信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_doom_council_info[终焉议会信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="25.25" customWidth="1" style="2" min="1" max="4"/>
@@ -1065,7 +1065,7 @@
           <t>success_rate</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>council_num</t>
         </is>
@@ -1127,7 +1127,7 @@
           <t>float</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1189,7 +1189,7 @@
           <t>通过率</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>议会人数(min,max)</t>
         </is>
@@ -1247,7 +1247,7 @@
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1290,7 +1290,7 @@
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1333,7 +1333,7 @@
       <c r="B6" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1378,7 +1378,7 @@
       <c r="B7" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1423,7 +1423,7 @@
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1469,7 +1469,7 @@
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1515,7 +1515,7 @@
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1561,7 +1561,7 @@
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1607,7 +1607,7 @@
       <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1653,7 +1653,7 @@
       <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1699,7 +1699,7 @@
       <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
@@ -1735,6 +1735,102 @@
       <c r="L14" s="1" t="inlineStr">
         <is>
           <t>想要转生成兽人！</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1000300001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ui_icon_1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DoomCouncilEntityEnemyIntensity</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1000300001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000300001</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>挑战更强的敌人！-下次征服敌人翻倍强(HP/护甲/攻击)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1000300002</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ui_icon_1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DoomCouncilEntityEnemyIntensity</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1000300002</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1000300002</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>挑战更弱的敌人！-下次征服敌人减半弱(HP/护甲/攻击)</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_doom_council_info[终焉议会信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_doom_council_info[终焉议会信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="25.25" customWidth="1" style="2" min="1" max="4"/>
@@ -1739,98 +1739,270 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>1000300001</v>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>ui_icon_1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>DoomCouncilEntityEnemyIntensity</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="1" t="n">
         <v>1000300001</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="1" t="n">
         <v>1000300001</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>挑战更强的敌人！-下次征服敌人翻倍强(HP/护甲/攻击)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>1000300002</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>ui_icon_1</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>DoomCouncilEntityEnemyIntensity</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="1" t="n">
         <v>1000300002</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="1" t="n">
         <v>1000300002</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>挑战更弱的敌人！-下次征服敌人减半弱(HP/护甲/攻击)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1000400001</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ui_icon_1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DoomCouncilEntityCreatureLevelDown</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100200005</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1000400001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1000400001</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>想要魔物等级下降！-魔物等级下降1级</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1000400002</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ui_icon_1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DoomCouncilEntityCreatureLevelDown</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100200006</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1000400002</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1000400002</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>想要魔物等级归0！-魔物等级下降到0级</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1000400003</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ui_icon_1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DoomCouncilEntityCreatureRarityDown</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100200007</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1000400003</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1000400003</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>想要魔物稀有度下降！-魔物稀有度下降1级</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1000400004</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ui_icon_1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DoomCouncilEntityCreatureRarityDown</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100200008</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1000400004</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1000400004</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>想要魔物稀有度归0！-魔物稀有度下降到N级</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_doom_council_info[终焉议会信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_doom_council_info[终焉议会信息].xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="25.25" customWidth="1" style="2" min="1" max="4"/>
@@ -1835,174 +1835,260 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>1000400001</v>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="D17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>ui_icon_1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>DoomCouncilEntityCreatureLevelDown</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="H17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>100200005</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="1" t="n">
         <v>1000400001</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="1" t="n">
         <v>1000400001</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="1" t="inlineStr">
         <is>
           <t>想要魔物等级下降！-魔物等级下降1级</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>1000400002</v>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="D18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>ui_icon_1</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>DoomCouncilEntityCreatureLevelDown</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="1" t="n">
         <v>100200006</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="1" t="n">
         <v>1000400002</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="1" t="n">
         <v>1000400002</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="1" t="inlineStr">
         <is>
           <t>想要魔物等级归0！-魔物等级下降到0级</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>1000400003</v>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="D19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>ui_icon_1</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>DoomCouncilEntityCreatureRarityDown</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="H19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>100200007</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="1" t="n">
         <v>1000400003</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19" s="1" t="n">
         <v>1000400003</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>想要魔物稀有度下降！-魔物稀有度下降1级</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>1000400004</v>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>20,20</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="D20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>ui_icon_1</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>DoomCouncilEntityCreatureRarityDown</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="1" t="n">
         <v>100200008</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="1" t="n">
         <v>1000400004</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="1" t="n">
         <v>1000400004</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t>想要魔物稀有度归0！-魔物稀有度下降到N级</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>1000500001</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>ui_icon_1</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>DoomCouncilEntityMoreEquip</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>100200009</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>1000500001</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>1000500001</v>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>想要更多装备！-下一次征服模式的通关奖励全部变为装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1000500002</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20,20</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ui_icon_1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DoomCouncilEntityMoreDemonLordEquip</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100200010</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1000500002</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000500002</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>想要更多魔王装备！-下一次征服模式的通关奖励全部变为魔王装备</t>
         </is>
       </c>
     </row>
